--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_022.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_022.xlsx
@@ -1199,7 +1199,7 @@
         <v>74</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>28</v>
@@ -1222,7 +1222,7 @@
         <v>76</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>28</v>
@@ -1245,7 +1245,7 @@
         <v>78</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>28</v>
@@ -1889,7 +1889,7 @@
         <v>74</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>89</v>
@@ -1912,7 +1912,7 @@
         <v>76</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>89</v>
@@ -1935,7 +1935,7 @@
         <v>78</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>89</v>
